--- a/ExamWritten_260408/ExamRegistration_IDMA26_NDAB23K02E.xlsx
+++ b/ExamWritten_260408/ExamRegistration_IDMA26_NDAB23K02E.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\SUN-FAK-Studienaevn-Eksamen\SCIENCE Nørre\5. Tilmeldingslister\2025-2026\Tilmeldingslister B3 ordinær\DIKU B3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Teaching\IDMA26\ExamWritten_260408\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8710CE7-798C-4665-9C88-476B5714FE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F139C533-E6BA-466C-B656-00B35449F0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21EEBF5E-C9AF-46AA-8FFE-87BB477D1A1C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{21EEBF5E-C9AF-46AA-8FFE-87BB477D1A1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="93">
   <si>
     <t>ADM</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>MF (Skriv MF hvis MF, ellers blank)</t>
+  </si>
+  <si>
+    <t>MF</t>
   </si>
 </sst>
 </file>
@@ -915,7 +918,9 @@
       <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1755,7 +1760,9 @@
       <c r="I34" t="s">
         <v>17</v>
       </c>
-      <c r="K34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
